--- a/docs/research/one-year-backtest.xlsx
+++ b/docs/research/one-year-backtest.xlsx
@@ -23,27 +23,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,13 +53,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -124,34 +119,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,28 +512,28 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>مقایسهٔ استخر با و بدون قانون ۷ (بولینگر + RSI)</t>
+          <t>گزارش یک‌سالهٔ استخر — با و بدون قانون ۷ (بولینگر + RSI)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>دورهٔ 365 روزه · قیمتِ ۵۰-۵۰ بدون اسپرد و کارمزد</t>
+          <t>دورهٔ 365 روزه · مارتینگل · قیمتِ ۵۰-۵۰ بدون اسپرد و کارمزد</t>
         </is>
       </c>
     </row>
@@ -556,27 +548,32 @@
           <t>سیگنال</t>
         </is>
       </c>
-      <c r="C4" s="4">
-        <f>SUM(روزانه!D2:D367)</f>
-        <v/>
+      <c r="C4" s="4" t="n">
+        <v>20661</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>دقت</t>
         </is>
       </c>
-      <c r="E4" s="5">
-        <f>SUM(روزانه!E2:E367)/C4</f>
-        <v/>
+      <c r="E4" s="5" t="n">
+        <v>0.5371472823193456</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>در روز</t>
         </is>
       </c>
-      <c r="G4" s="6">
-        <f>C4/365</f>
-        <v/>
+      <c r="G4" s="6" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>در ماه</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1698</v>
       </c>
     </row>
     <row r="5">
@@ -590,27 +587,32 @@
           <t>سیگنال</t>
         </is>
       </c>
-      <c r="C5" s="4">
-        <f>SUM(روزانه!L2:L367)</f>
-        <v/>
+      <c r="C5" s="4" t="n">
+        <v>21303</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>دقت</t>
         </is>
       </c>
-      <c r="E5" s="5">
-        <f>SUM(روزانه!M2:M367)/C5</f>
-        <v/>
+      <c r="E5" s="5" t="n">
+        <v>0.5381401680514482</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>در روز</t>
         </is>
       </c>
-      <c r="G5" s="6">
-        <f>C5/365</f>
-        <v/>
+      <c r="G5" s="6" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>در ماه</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1751</v>
       </c>
     </row>
     <row r="7">
@@ -673,34 +675,29 @@
           <t>3 پله · 20$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B9" s="9">
-        <f>SUM(روزانه!F2:F367)</f>
-        <v/>
-      </c>
-      <c r="C9" s="9">
-        <f>B9/365*30</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>B9/365*7</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>B9/365*1</f>
-        <v/>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="B9" s="9" t="n">
+        <v>56060</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>4608</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>154</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>2040</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="9" t="n">
         <v>-1300</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="4" t="n">
         <v>1185</v>
       </c>
-      <c r="I9" s="6">
-        <f>IF(F9=0,0,B9/F9)</f>
-        <v/>
+      <c r="I9" s="6" t="n">
+        <v>27.5</v>
       </c>
     </row>
     <row r="10">
@@ -709,34 +706,29 @@
           <t>4 پله · 20$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B10" s="9">
-        <f>SUM(روزانه!G2:G367)</f>
-        <v/>
-      </c>
-      <c r="C10" s="9">
-        <f>B10/365*30</f>
-        <v/>
-      </c>
-      <c r="D10" s="9">
-        <f>B10/365*7</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>B10/365*1</f>
-        <v/>
-      </c>
-      <c r="F10" s="10" t="n">
+      <c r="B10" s="9" t="n">
+        <v>65060</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>5347</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1248</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>4340</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="9" t="n">
         <v>-1880</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="4" t="n">
         <v>523</v>
       </c>
-      <c r="I10" s="6">
-        <f>IF(F10=0,0,B10/F10)</f>
-        <v/>
+      <c r="I10" s="6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -745,34 +737,29 @@
           <t>5 پله · 20$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B11" s="9">
-        <f>SUM(روزانه!H2:H367)</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>B11/365*30</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>B11/365*7</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>B11/365*1</f>
-        <v/>
-      </c>
-      <c r="F11" s="10" t="n">
+      <c r="B11" s="9" t="n">
+        <v>76260</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>6268</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="F11" s="9" t="n">
         <v>3300</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="9" t="n">
         <v>-1100</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="I11" s="6">
-        <f>IF(F11=0,0,B11/F11)</f>
-        <v/>
+      <c r="I11" s="6" t="n">
+        <v>23.1</v>
       </c>
     </row>
     <row r="12">
@@ -781,34 +768,29 @@
           <t>3 پله · 50$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B12" s="9">
-        <f>SUM(روزانه!I2:I367)</f>
-        <v/>
-      </c>
-      <c r="C12" s="9">
-        <f>B12/365*30</f>
-        <v/>
-      </c>
-      <c r="D12" s="9">
-        <f>B12/365*7</f>
-        <v/>
-      </c>
-      <c r="E12" s="9">
-        <f>B12/365*1</f>
-        <v/>
-      </c>
-      <c r="F12" s="10" t="n">
+      <c r="B12" s="9" t="n">
+        <v>140150</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>11519</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2688</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>5100</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>-3250</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="4" t="n">
         <v>1185</v>
       </c>
-      <c r="I12" s="6">
-        <f>IF(F12=0,0,B12/F12)</f>
-        <v/>
+      <c r="I12" s="6" t="n">
+        <v>27.5</v>
       </c>
     </row>
     <row r="13">
@@ -817,34 +799,29 @@
           <t>4 پله · 50$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B13" s="9">
-        <f>SUM(روزانه!J2:J367)</f>
-        <v/>
-      </c>
-      <c r="C13" s="9">
-        <f>B13/365*30</f>
-        <v/>
-      </c>
-      <c r="D13" s="9">
-        <f>B13/365*7</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>B13/365*1</f>
-        <v/>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="B13" s="9" t="n">
+        <v>162650</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>13368</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>3119</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>10850</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="9" t="n">
         <v>-4700</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="4" t="n">
         <v>523</v>
       </c>
-      <c r="I13" s="6">
-        <f>IF(F13=0,0,B13/F13)</f>
-        <v/>
+      <c r="I13" s="6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -853,263 +830,228 @@
           <t>5 پله · 50$ · بدون قانون ۷</t>
         </is>
       </c>
-      <c r="B14" s="9">
-        <f>SUM(روزانه!K2:K367)</f>
-        <v/>
-      </c>
-      <c r="C14" s="9">
-        <f>B14/365*30</f>
-        <v/>
-      </c>
-      <c r="D14" s="9">
-        <f>B14/365*7</f>
-        <v/>
-      </c>
-      <c r="E14" s="9">
-        <f>B14/365*1</f>
-        <v/>
-      </c>
-      <c r="F14" s="10" t="n">
+      <c r="B14" s="9" t="n">
+        <v>190650</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>15670</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>3656</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>522</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>8250</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <v>-2750</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="I14" s="6">
-        <f>IF(F14=0,0,B14/F14)</f>
-        <v/>
+      <c r="I14" s="6" t="n">
+        <v>23.1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>3 پله · 20$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B15" s="13">
-        <f>SUM(روزانه!N2:N367)</f>
-        <v/>
-      </c>
-      <c r="C15" s="13">
-        <f>B15/365*30</f>
-        <v/>
-      </c>
-      <c r="D15" s="13">
-        <f>B15/365*7</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15/365*1</f>
-        <v/>
-      </c>
-      <c r="F15" s="14" t="n">
+      <c r="B15" s="11" t="n">
+        <v>59460</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>4887</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>163</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>1720</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="11" t="n">
         <v>-900</v>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="12" t="n">
         <v>1213</v>
       </c>
-      <c r="I15" s="16">
-        <f>IF(F15=0,0,B15/F15)</f>
-        <v/>
+      <c r="I15" s="13" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>4 پله · 20$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B16" s="13">
-        <f>SUM(روزانه!O2:O367)</f>
-        <v/>
-      </c>
-      <c r="C16" s="13">
-        <f>B16/365*30</f>
-        <v/>
-      </c>
-      <c r="D16" s="13">
-        <f>B16/365*7</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16/365*1</f>
-        <v/>
-      </c>
-      <c r="F16" s="14" t="n">
+      <c r="B16" s="11" t="n">
+        <v>69080</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>5678</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>189</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>4020</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="11" t="n">
         <v>-1620</v>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" s="12" t="n">
         <v>534</v>
       </c>
-      <c r="I16" s="16">
-        <f>IF(F16=0,0,B16/F16)</f>
-        <v/>
+      <c r="I16" s="13" t="n">
+        <v>17.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>5 پله · 20$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>SUM(روزانه!P2:P367)</f>
-        <v/>
-      </c>
-      <c r="C17" s="13">
-        <f>B17/365*30</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>B17/365*7</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17/365*1</f>
-        <v/>
-      </c>
-      <c r="F17" s="14" t="n">
+      <c r="B17" s="11" t="n">
+        <v>81100</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>6666</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1555</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>222</v>
+      </c>
+      <c r="F17" s="11" t="n">
         <v>4000</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="11" t="n">
         <v>-1000</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="I17" s="16">
-        <f>IF(F17=0,0,B17/F17)</f>
-        <v/>
+      <c r="I17" s="13" t="n">
+        <v>20.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>3 پله · 50$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B18" s="13">
-        <f>SUM(روزانه!Q2:Q367)</f>
-        <v/>
-      </c>
-      <c r="C18" s="13">
-        <f>B18/365*30</f>
-        <v/>
-      </c>
-      <c r="D18" s="13">
-        <f>B18/365*7</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18/365*1</f>
-        <v/>
-      </c>
-      <c r="F18" s="14" t="n">
+      <c r="B18" s="11" t="n">
+        <v>148650</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>12218</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2851</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>407</v>
+      </c>
+      <c r="F18" s="11" t="n">
         <v>4300</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="11" t="n">
         <v>-2250</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="12" t="n">
         <v>1213</v>
       </c>
-      <c r="I18" s="16">
-        <f>IF(F18=0,0,B18/F18)</f>
-        <v/>
+      <c r="I18" s="13" t="n">
+        <v>34.6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>4 پله · 50$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B19" s="13">
-        <f>SUM(روزانه!R2:R367)</f>
-        <v/>
-      </c>
-      <c r="C19" s="13">
-        <f>B19/365*30</f>
-        <v/>
-      </c>
-      <c r="D19" s="13">
-        <f>B19/365*7</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19/365*1</f>
-        <v/>
-      </c>
-      <c r="F19" s="14" t="n">
+      <c r="B19" s="11" t="n">
+        <v>172700</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>14195</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>3312</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>473</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>10050</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="11" t="n">
         <v>-4050</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="12" t="n">
         <v>534</v>
       </c>
-      <c r="I19" s="16">
-        <f>IF(F19=0,0,B19/F19)</f>
-        <v/>
+      <c r="I19" s="13" t="n">
+        <v>17.2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>5 پله · 50$ · با قانون ۷</t>
         </is>
       </c>
-      <c r="B20" s="13">
-        <f>SUM(روزانه!S2:S367)</f>
-        <v/>
-      </c>
-      <c r="C20" s="13">
-        <f>B20/365*30</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>B20/365*7</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20/365*1</f>
-        <v/>
-      </c>
-      <c r="F20" s="14" t="n">
+      <c r="B20" s="11" t="n">
+        <v>202750</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>16664</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>3888</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>555</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="11" t="n">
         <v>-2500</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="I20" s="16">
-        <f>IF(F20=0,0,B20/F20)</f>
-        <v/>
+      <c r="I20" s="13" t="n">
+        <v>20.3</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>سلول‌های آبی خروجی شبیه‌سازی‌اند (مسیر-وابسته). بقیه فرمول‌اند و از شیت «روزانه» می‌آیند.</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>قانون ۷ در 642 پنجره تنها بود و در 0 پنجره خلافِ استخر گفت.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>قانون ۷ در 642 پنجره تنها بود و در 0 پنجره خلافِ استخر گفت.</t>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>همهٔ اعداد خروجیِ شبیه‌سازیِ کندل‌به‌کندل‌اند و ثابت — این گزارشِ تاریخی است، نه مدلِ زنده.</t>
         </is>
       </c>
     </row>
@@ -1149,97 +1091,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>روز هفته</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>ماه</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>برد (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>3 پله/20$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>4 پله/20$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>5 پله/20$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>3 پله/50$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>4 پله/50$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>5 پله/50$ (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (با قانون ۷)</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>برد (با قانون ۷)</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>3 پله/20$ (با قانون ۷)</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>4 پله/20$ (با قانون ۷)</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>5 پله/20$ (با قانون ۷)</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>3 پله/50$ (با قانون ۷)</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>4 پله/50$ (با قانون ۷)</t>
         </is>
       </c>
-      <c r="S1" s="18" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>5 پله/50$ (با قانون ۷)</t>
         </is>
@@ -25059,37 +25001,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ساعت ET</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>برد (بدون قانون ۷)</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>در روز (بدون قانون ۷)</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>دقت (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (با قانون ۷)</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>برد (با قانون ۷)</t>
-        </is>
-      </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>در روز (با قانون ۷)</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>دقت (با قانون ۷)</t>
         </is>
@@ -25099,600 +25041,552 @@
       <c r="A2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="4" t="n">
         <v>613</v>
       </c>
-      <c r="C2" s="11" t="n">
-        <v>321</v>
-      </c>
-      <c r="D2" s="5">
-        <f>IF(B2=0,0,C2/B2)</f>
-        <v/>
-      </c>
-      <c r="E2" s="11" t="n">
+      <c r="C2" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.5236541598694943</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>638</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>338</v>
-      </c>
-      <c r="G2" s="5">
-        <f>IF(E2=0,0,F2/E2)</f>
-        <v/>
+      <c r="F2" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.5297805642633229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="4" t="n">
         <v>624</v>
       </c>
-      <c r="C3" s="11" t="n">
-        <v>339</v>
-      </c>
-      <c r="D3" s="5">
-        <f>IF(B3=0,0,C3/B3)</f>
-        <v/>
-      </c>
-      <c r="E3" s="11" t="n">
+      <c r="C3" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0.5432692307692307</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>666</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>364</v>
-      </c>
-      <c r="G3" s="5">
-        <f>IF(E3=0,0,F3/E3)</f>
-        <v/>
+      <c r="F3" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.5465465465465466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="4" t="n">
         <v>651</v>
       </c>
-      <c r="C4" s="11" t="n">
-        <v>357</v>
-      </c>
-      <c r="D4" s="5">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="C4" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>698</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>390</v>
-      </c>
-      <c r="G4" s="5">
-        <f>IF(E4=0,0,F4/E4)</f>
-        <v/>
+      <c r="F4" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.5587392550143266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="4" t="n">
         <v>725</v>
       </c>
-      <c r="C5" s="11" t="n">
-        <v>375</v>
-      </c>
-      <c r="D5" s="5">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="C5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>771</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>404</v>
-      </c>
-      <c r="G5" s="5">
-        <f>IF(E5=0,0,F5/E5)</f>
-        <v/>
+      <c r="F5" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.5239948119325551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="4" t="n">
         <v>776</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>420</v>
-      </c>
-      <c r="D6" s="5">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="C6" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5412371134020618</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>812</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>439</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(E6=0,0,F6/E6)</f>
-        <v/>
+      <c r="F6" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5406403940886699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="4" t="n">
         <v>835</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>464</v>
-      </c>
-      <c r="D7" s="5">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="C7" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.555688622754491</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>861</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>477</v>
-      </c>
-      <c r="G7" s="5">
-        <f>IF(E7=0,0,F7/E7)</f>
-        <v/>
+      <c r="F7" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.554006968641115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="4" t="n">
         <v>743</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>384</v>
-      </c>
-      <c r="D8" s="5">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="11" t="n">
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5168236877523553</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>771</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>401</v>
-      </c>
-      <c r="G8" s="5">
-        <f>IF(E8=0,0,F8/E8)</f>
-        <v/>
+      <c r="F8" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.5201037613488976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="4" t="n">
         <v>769</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>415</v>
-      </c>
-      <c r="D9" s="5">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="11" t="n">
+      <c r="C9" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5396618985695709</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>803</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>434</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(E9=0,0,F9/E9)</f>
-        <v/>
+      <c r="F9" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.5404732254047323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="4" t="n">
         <v>1010</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>551</v>
-      </c>
-      <c r="D10" s="5">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="11" t="n">
+      <c r="C10" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5455445544554456</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>1029</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>563</v>
-      </c>
-      <c r="G10" s="5">
-        <f>IF(E10=0,0,F10/E10)</f>
-        <v/>
+      <c r="F10" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.5471331389698737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="4" t="n">
         <v>1434</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>772</v>
-      </c>
-      <c r="D11" s="5">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="C11" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5383542538354253</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>1448</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>780</v>
-      </c>
-      <c r="G11" s="5">
-        <f>IF(E11=0,0,F11/E11)</f>
-        <v/>
+      <c r="F11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.5386740331491713</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="4" t="n">
         <v>1690</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>879</v>
-      </c>
-      <c r="D12" s="5">
-        <f>IF(B12=0,0,C12/B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="C12" s="6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5201183431952663</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>1698</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>884</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(E12=0,0,F12/E12)</f>
-        <v/>
+      <c r="F12" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.5206124852767963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="4" t="n">
         <v>1555</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>824</v>
-      </c>
-      <c r="D13" s="5">
-        <f>IF(B13=0,0,C13/B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="C13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5299035369774919</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>1559</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>825</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(E13=0,0,F13/E13)</f>
-        <v/>
+      <c r="F13" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.5291853752405388</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="4" t="n">
         <v>1145</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>635</v>
-      </c>
-      <c r="D14" s="5">
-        <f>IF(B14=0,0,C14/B14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="C14" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5545851528384279</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>1152</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>639</v>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(E14=0,0,F14/E14)</f>
-        <v/>
+      <c r="F14" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.5546875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="4" t="n">
         <v>1032</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>542</v>
-      </c>
-      <c r="D15" s="5">
-        <f>IF(B15=0,0,C15/B15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="11" t="n">
+      <c r="C15" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5251937984496124</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>1047</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>551</v>
-      </c>
-      <c r="G15" s="5">
-        <f>IF(E15=0,0,F15/E15)</f>
-        <v/>
+      <c r="F15" s="6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.5262655205348615</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="4" t="n">
         <v>745</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>422</v>
-      </c>
-      <c r="D16" s="5">
-        <f>IF(B16=0,0,C16/B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="11" t="n">
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5664429530201343</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>762</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>433</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(E16=0,0,F16/E16)</f>
-        <v/>
+      <c r="F16" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.568241469816273</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="4" t="n">
         <v>630</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>335</v>
-      </c>
-      <c r="D17" s="5">
-        <f>IF(B17=0,0,C17/B17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="C17" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5317460317460317</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>657</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>346</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(E17=0,0,F17/E17)</f>
-        <v/>
+      <c r="F17" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.5266362252663622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="4" t="n">
         <v>556</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>287</v>
-      </c>
-      <c r="D18" s="5">
-        <f>IF(B18=0,0,C18/B18)</f>
-        <v/>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="C18" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5161870503597122</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>581</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>301</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(E18=0,0,F18/E18)</f>
-        <v/>
+      <c r="F18" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.5180722891566265</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>278</v>
-      </c>
-      <c r="D19" s="5">
-        <f>IF(B19=0,0,C19/B19)</f>
-        <v/>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="C19" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.5720164609053497</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>539</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>312</v>
-      </c>
-      <c r="G19" s="5">
-        <f>IF(E19=0,0,F19/E19)</f>
-        <v/>
+      <c r="F19" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.5788497217068646</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="4" t="n">
         <v>643</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>361</v>
-      </c>
-      <c r="D20" s="5">
-        <f>IF(B20=0,0,C20/B20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="11" t="n">
+      <c r="C20" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.5614307931570762</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>678</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>381</v>
-      </c>
-      <c r="G20" s="5">
-        <f>IF(E20=0,0,F20/E20)</f>
-        <v/>
+      <c r="F20" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.5619469026548672</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="4" t="n">
         <v>644</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>353</v>
-      </c>
-      <c r="D21" s="5">
-        <f>IF(B21=0,0,C21/B21)</f>
-        <v/>
-      </c>
-      <c r="E21" s="11" t="n">
+      <c r="C21" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.5481366459627329</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>676</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>369</v>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(E21=0,0,F21/E21)</f>
-        <v/>
+      <c r="F21" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.5458579881656804</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="4" t="n">
         <v>795</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>414</v>
-      </c>
-      <c r="D22" s="5">
-        <f>IF(B22=0,0,C22/B22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="11" t="n">
+      <c r="C22" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.5207547169811321</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>823</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>425</v>
-      </c>
-      <c r="G22" s="5">
-        <f>IF(E22=0,0,F22/E22)</f>
-        <v/>
+      <c r="F22" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.5164034021871203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="4" t="n">
         <v>941</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>516</v>
-      </c>
-      <c r="D23" s="5">
-        <f>IF(B23=0,0,C23/B23)</f>
-        <v/>
-      </c>
-      <c r="E23" s="11" t="n">
+      <c r="C23" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.5483528161530287</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>969</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>533</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(E23=0,0,F23/E23)</f>
-        <v/>
+      <c r="F23" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.5500515995872033</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="4" t="n">
         <v>847</v>
       </c>
-      <c r="C24" s="11" t="n">
-        <v>465</v>
-      </c>
-      <c r="D24" s="5">
-        <f>IF(B24=0,0,C24/B24)</f>
-        <v/>
-      </c>
-      <c r="E24" s="11" t="n">
+      <c r="C24" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.5489964580873672</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>863</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>473</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(E24=0,0,F24/E24)</f>
-        <v/>
+      <c r="F24" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.5480880648899189</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="4" t="n">
         <v>772</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>389</v>
-      </c>
-      <c r="D25" s="5">
-        <f>IF(B25=0,0,C25/B25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="11" t="n">
+      <c r="C25" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.5038860103626943</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>802</v>
       </c>
-      <c r="F25" s="11" t="n">
-        <v>402</v>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(E25=0,0,F25/E25)</f>
-        <v/>
+      <c r="F25" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.5012468827930174</v>
       </c>
     </row>
   </sheetData>
@@ -25712,58 +25606,58 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>روز هفته</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>دقت (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۲۰$ (بدون قانون ۷)</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۵۰$ (بدون قانون ۷)</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۲۰$ (بدون قانون ۷)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۵۰$ (بدون قانون ۷)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (با قانون ۷)</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>دقت (با قانون ۷)</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۲۰$ (با قانون ۷)</t>
-        </is>
-      </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۵۰$ (با قانون ۷)</t>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۲۰$ (با قانون ۷)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۵۰$ (با قانون ۷)</t>
         </is>
       </c>
     </row>
@@ -25773,37 +25667,29 @@
           <t>دوشنبه</t>
         </is>
       </c>
-      <c r="B2" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C2" s="5">
-        <f>IF(B2=0,0,SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$E$2:$E$367)/B2)</f>
-        <v/>
-      </c>
-      <c r="D2" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E2" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F2" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G2" s="5">
-        <f>IF(F2=0,0,SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$M$2:$M$367)/F2)</f>
-        <v/>
-      </c>
-      <c r="H2" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I2" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A2,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B2" s="4" t="n">
+        <v>2669</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.5402772573997752</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>7060</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>17650</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>2766</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.5430224150397687</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -25812,37 +25698,29 @@
           <t>سه‌شنبه</t>
         </is>
       </c>
-      <c r="B3" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C3" s="5">
-        <f>IF(B3=0,0,SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$E$2:$E$367)/B3)</f>
-        <v/>
-      </c>
-      <c r="D3" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F3" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>IF(F3=0,0,SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$M$2:$M$367)/F3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I3" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A3,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B3" s="4" t="n">
+        <v>2897</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.5398688298239558</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>6680</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>16700</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2979</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.5391070829137294</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>6540</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>16350</v>
       </c>
     </row>
     <row r="4">
@@ -25851,37 +25729,29 @@
           <t>چهارشنبه</t>
         </is>
       </c>
-      <c r="B4" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C4" s="5">
-        <f>IF(B4=0,0,SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$E$2:$E$367)/B4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E4" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F4" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
-        <f>IF(F4=0,0,SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$M$2:$M$367)/F4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I4" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A4,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B4" s="4" t="n">
+        <v>2998</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.529352901934623</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>7880</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>19700</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>3109</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.5310389192666453</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>8620</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>21550</v>
       </c>
     </row>
     <row r="5">
@@ -25890,37 +25760,29 @@
           <t>پنج‌شنبه</t>
         </is>
       </c>
-      <c r="B5" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>IF(B5=0,0,SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$E$2:$E$367)/B5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
-        <f>IF(F5=0,0,SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$M$2:$M$367)/F5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I5" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A5,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B5" s="4" t="n">
+        <v>2919</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5378554299417608</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>19950</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2992</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.5397727272727273</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>8460</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>21150</v>
       </c>
     </row>
     <row r="6">
@@ -25929,37 +25791,29 @@
           <t>جمعه</t>
         </is>
       </c>
-      <c r="B6" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>IF(B6=0,0,SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$E$2:$E$367)/B6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F6" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(F6=0,0,SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$M$2:$M$367)/F6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I6" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A6,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B6" s="4" t="n">
+        <v>2656</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5218373493975904</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>4080</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5248380129589633</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>4520</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>11300</v>
       </c>
     </row>
     <row r="7">
@@ -25968,37 +25822,29 @@
           <t>شنبه</t>
         </is>
       </c>
-      <c r="B7" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>IF(B7=0,0,SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$E$2:$E$367)/B7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F7" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>IF(F7=0,0,SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$M$2:$M$367)/F7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I7" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A7,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B7" s="4" t="n">
+        <v>2921</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5559739815131804</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3008</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.5558510638297872</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>29750</v>
       </c>
     </row>
     <row r="8">
@@ -26007,37 +25853,29 @@
           <t>یکشنبه</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
-        <f>IF(B8=0,0,SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$E$2:$E$367)/B8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>IF(F8=0,0,SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$M$2:$M$367)/F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I8" s="9">
-        <f>SUMIF(روزانه!$B$2:$B$367,$A8,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B8" s="4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5345737295195779</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>11580</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>28950</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3671</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.5339144647235086</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>11420</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>28550</v>
       </c>
     </row>
   </sheetData>
@@ -26057,58 +25895,58 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ماهانه</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>دقت (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۲۰$ (بدون قانون ۷)</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۵۰$ (بدون قانون ۷)</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۲۰$ (بدون قانون ۷)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۵۰$ (بدون قانون ۷)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>سیگنال (با قانون ۷)</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>دقت (با قانون ۷)</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۲۰$ (با قانون ۷)</t>
-        </is>
-      </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t>سود ۳پله/۵۰$ (با قانون ۷)</t>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۲۰$ (با قانون ۷)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>۳پله/۵۰$ (با قانون ۷)</t>
         </is>
       </c>
     </row>
@@ -26118,37 +25956,29 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B2" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C2" s="5">
-        <f>IF(B2=0,0,SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$E$2:$E$367)/B2)</f>
-        <v/>
-      </c>
-      <c r="D2" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E2" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F2" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G2" s="5">
-        <f>IF(F2=0,0,SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$M$2:$M$367)/F2)</f>
-        <v/>
-      </c>
-      <c r="H2" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I2" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A2,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B2" s="4" t="n">
+        <v>452</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.4778761061946903</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>459</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>-400</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>-1000</v>
       </c>
     </row>
     <row r="3">
@@ -26157,37 +25987,29 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B3" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C3" s="5">
-        <f>IF(B3=0,0,SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$E$2:$E$367)/B3)</f>
-        <v/>
-      </c>
-      <c r="D3" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E3" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F3" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>IF(F3=0,0,SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$M$2:$M$367)/F3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I3" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A3,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B3" s="4" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.5049332559489262</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>1360</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1777</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.505908835115363</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>4150</v>
       </c>
     </row>
     <row r="4">
@@ -26196,37 +26018,29 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B4" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C4" s="5">
-        <f>IF(B4=0,0,SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$E$2:$E$367)/B4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E4" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F4" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
-        <f>IF(F4=0,0,SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$M$2:$M$367)/F4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I4" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A4,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B4" s="4" t="n">
+        <v>1763</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4968803176403857</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>440</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1809</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.4969596462133776</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>340</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="5">
@@ -26235,37 +26049,29 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B5" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>IF(B5=0,0,SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$E$2:$E$367)/B5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
-        <f>IF(F5=0,0,SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$M$2:$M$367)/F5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I5" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A5,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B5" s="4" t="n">
+        <v>1644</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5431873479318735</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>12750</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1718</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.5459837019790454</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>6420</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>16050</v>
       </c>
     </row>
     <row r="6">
@@ -26274,37 +26080,29 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B6" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>IF(B6=0,0,SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$E$2:$E$367)/B6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F6" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(F6=0,0,SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$M$2:$M$367)/F6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I6" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A6,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B6" s="4" t="n">
+        <v>1562</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5268886043533931</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>3320</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>8300</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1618</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5284301606922126</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3120</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="7">
@@ -26313,37 +26111,29 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B7" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>IF(B7=0,0,SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$E$2:$E$367)/B7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F7" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>IF(F7=0,0,SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$M$2:$M$367)/F7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I7" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A7,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B7" s="4" t="n">
+        <v>1716</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.548951048951049</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>5680</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>14200</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1766</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.5498301245753114</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>14250</v>
       </c>
     </row>
     <row r="8">
@@ -26352,37 +26142,29 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
-        <f>IF(B8=0,0,SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$E$2:$E$367)/B8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>IF(F8=0,0,SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$M$2:$M$367)/F8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I8" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A8,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B8" s="4" t="n">
+        <v>1834</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5321701199563795</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>12750</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1881</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.5337586390217969</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>5240</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>13100</v>
       </c>
     </row>
     <row r="9">
@@ -26391,37 +26173,29 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B9" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C9" s="5">
-        <f>IF(B9=0,0,SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$E$2:$E$367)/B9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E9" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F9" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(F9=0,0,SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$M$2:$M$367)/F9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I9" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A9,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B9" s="4" t="n">
+        <v>1484</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5525606469002695</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>7580</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>18950</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.5549019607843138</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>7180</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>17950</v>
       </c>
     </row>
     <row r="10">
@@ -26430,37 +26204,29 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B10" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C10" s="5">
-        <f>IF(B10=0,0,SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$E$2:$E$367)/B10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F10" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>IF(F10=0,0,SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$M$2:$M$367)/F10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I10" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A10,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B10" s="4" t="n">
+        <v>1849</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5467820443482964</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>5940</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>14850</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1899</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.5476566614007372</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>6520</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="11">
@@ -26469,37 +26235,29 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B11" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C11" s="5">
-        <f>IF(B11=0,0,SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$E$2:$E$367)/B11)</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F11" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G11" s="5">
-        <f>IF(F11=0,0,SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$M$2:$M$367)/F11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I11" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A11,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B11" s="4" t="n">
+        <v>1691</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5623891188645772</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>6820</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>17050</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1736</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.5645161290322581</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>7680</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>19200</v>
       </c>
     </row>
     <row r="12">
@@ -26508,37 +26266,29 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B12" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C12" s="5">
-        <f>IF(B12=0,0,SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$E$2:$E$367)/B12)</f>
-        <v/>
-      </c>
-      <c r="D12" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E12" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F12" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(F12=0,0,SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$M$2:$M$367)/F12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I12" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A12,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B12" s="4" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5513513513513514</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>5300</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>13250</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1906</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.5514165792235047</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>6060</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>15150</v>
       </c>
     </row>
     <row r="13">
@@ -26547,37 +26297,29 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B13" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C13" s="5">
-        <f>IF(B13=0,0,SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$E$2:$E$367)/B13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(F13=0,0,SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$M$2:$M$367)/F13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I13" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A13,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B13" s="4" t="n">
+        <v>1734</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5403690888119954</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>5020</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>12550</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1797</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.5414579855314413</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>5180</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>12950</v>
       </c>
     </row>
     <row r="14">
@@ -26586,37 +26328,29 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B14" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$D$2:$D$367)</f>
-        <v/>
-      </c>
-      <c r="C14" s="5">
-        <f>IF(B14=0,0,SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$E$2:$E$367)/B14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$F$2:$F$367)</f>
-        <v/>
-      </c>
-      <c r="E14" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$I$2:$I$367)</f>
-        <v/>
-      </c>
-      <c r="F14" s="4">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$L$2:$L$367)</f>
-        <v/>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(F14=0,0,SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$M$2:$M$367)/F14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$N$2:$N$367)</f>
-        <v/>
-      </c>
-      <c r="I14" s="9">
-        <f>SUMIF(روزانه!$C$2:$C$367,$A14,روزانه!$Q$2:$Q$367)</f>
-        <v/>
+      <c r="B14" s="4" t="n">
+        <v>1359</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5614422369389257</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>4900</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>12250</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1407</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.5572139303482587</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>4760</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>11900</v>
       </c>
     </row>
   </sheetData>
@@ -26641,27 +26375,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>طول رشته</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>تعداد (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>درصد (بدون قانون ۷)</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>تعداد (با قانون ۷)</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>درصد (با قانون ۷)</t>
         </is>
@@ -26671,228 +26405,204 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="4" t="n">
         <v>2883</v>
       </c>
-      <c r="C2" s="5">
-        <f>B2/5229</f>
-        <v/>
-      </c>
-      <c r="D2" s="11" t="n">
+      <c r="C2" s="5" t="n">
+        <v>0.5513482501434309</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>2983</v>
       </c>
-      <c r="E2" s="5">
-        <f>D2/5395</f>
-        <v/>
+      <c r="E2" s="5" t="n">
+        <v>0.5529193697868396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="4" t="n">
         <v>1290</v>
       </c>
-      <c r="C3" s="5">
-        <f>B3/5229</f>
-        <v/>
-      </c>
-      <c r="D3" s="11" t="n">
+      <c r="C3" s="5" t="n">
+        <v>0.246701090074584</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>1331</v>
       </c>
-      <c r="E3" s="5">
-        <f>D3/5395</f>
-        <v/>
+      <c r="E3" s="5" t="n">
+        <v>0.2467099165894347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="4" t="n">
         <v>562</v>
       </c>
-      <c r="C4" s="5">
-        <f>B4/5229</f>
-        <v/>
-      </c>
-      <c r="D4" s="11" t="n">
+      <c r="C4" s="5" t="n">
+        <v>0.1074775291642762</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>578</v>
       </c>
-      <c r="E4" s="5">
-        <f>D4/5395</f>
-        <v/>
+      <c r="E4" s="5" t="n">
+        <v>0.1071362372567192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="C5" s="5">
-        <f>B5/5229</f>
-        <v/>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="C5" s="5" t="n">
+        <v>0.05048766494549627</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>269</v>
       </c>
-      <c r="E5" s="5">
-        <f>D5/5395</f>
-        <v/>
+      <c r="E5" s="5" t="n">
+        <v>0.04986098239110287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="C6" s="5">
-        <f>B6/5229</f>
-        <v/>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="C6" s="5" t="n">
+        <v>0.02294893861158922</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="E6" s="5">
-        <f>D6/5395</f>
-        <v/>
+      <c r="E6" s="5" t="n">
+        <v>0.02261353104726599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="C7" s="5">
-        <f>B7/5229</f>
-        <v/>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="5" t="n">
+        <v>0.01262191623637407</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="E7" s="5">
-        <f>D7/5395</f>
-        <v/>
+      <c r="E7" s="5" t="n">
+        <v>0.01241890639481001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C8" s="5">
-        <f>B8/5229</f>
-        <v/>
-      </c>
-      <c r="D8" s="11" t="n">
+      <c r="C8" s="5" t="n">
+        <v>0.003633581946834959</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E8" s="5">
-        <f>D8/5395</f>
-        <v/>
+      <c r="E8" s="5" t="n">
+        <v>0.003336422613531047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="5">
-        <f>B9/5229</f>
-        <v/>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="5" t="n">
+        <v>0.001912411550965768</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E9" s="5">
-        <f>D9/5395</f>
-        <v/>
+      <c r="E9" s="5" t="n">
+        <v>0.002038924930491195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
-        <f>B10/5229</f>
-        <v/>
-      </c>
-      <c r="D10" s="11" t="n">
+      <c r="C10" s="5" t="n">
+        <v>0.001912411550965768</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E10" s="5">
-        <f>D10/5395</f>
-        <v/>
+      <c r="E10" s="5" t="n">
+        <v>0.002038924930491195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5">
-        <f>B11/5229</f>
-        <v/>
-      </c>
-      <c r="D11" s="11" t="n">
+      <c r="C11" s="5" t="n">
+        <v>0.0001912411550965768</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="5">
-        <f>D11/5395</f>
-        <v/>
+      <c r="E11" s="5" t="n">
+        <v>0.000185356811862836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="5">
-        <f>B12/5229</f>
-        <v/>
-      </c>
-      <c r="D12" s="11" t="n">
+      <c r="C12" s="5" t="n">
+        <v>0.0005737234652897303</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="5">
-        <f>D12/5395</f>
-        <v/>
+      <c r="E12" s="5" t="n">
+        <v>0.0005560704355885078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="5">
-        <f>B13/5229</f>
-        <v/>
-      </c>
-      <c r="D13" s="11" t="n">
+      <c r="C13" s="5" t="n">
+        <v>0.0001912411550965768</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="5">
-        <f>D13/5395</f>
-        <v/>
+      <c r="E13" s="5" t="n">
+        <v>0.000185356811862836</v>
       </c>
     </row>
   </sheetData>
@@ -26919,213 +26629,213 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>سرمایه</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>آرایش</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>پایه</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>پله</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>نتیجه</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>تاریخ صفر شدن</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>بدترین افت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="n">
+      <c r="A2" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="G2" s="19" t="n">
+      <c r="G2" s="16" t="n">
         <v>1620</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="16" t="n">
         <v>1760</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>2025-07-27</t>
         </is>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="16" t="n">
         <v>1460</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="16" t="n">
         <v>2600</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="16" t="n">
         <v>2950</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="16" t="n">
         <v>1550</v>
       </c>
     </row>
@@ -27144,7 +26854,7 @@
       <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27155,147 +26865,147 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="16" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="16" t="n">
         <v>1480</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="16" t="n">
         <v>2750</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="16" t="n">
         <v>3050</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="16" t="n">
         <v>1000</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="16" t="n">
         <v>1550</v>
       </c>
     </row>
@@ -27314,7 +27024,7 @@
       <c r="D14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27325,31 +27035,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="16" t="n">
         <v>2540</v>
       </c>
     </row>
@@ -27368,7 +27078,7 @@
       <c r="D16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27379,89 +27089,89 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="16" t="n">
         <v>3450</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="16" t="n">
         <v>3950</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>2025-07-27</t>
         </is>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="16" t="n">
         <v>3400</v>
       </c>
     </row>
@@ -27480,7 +27190,7 @@
       <c r="D20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27505,7 +27215,7 @@
       <c r="D21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27530,7 +27240,7 @@
       <c r="D22" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27541,89 +27251,89 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="16" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="16" t="n">
         <v>3900</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="16" t="n">
         <v>1800</v>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>2025-07-27</t>
         </is>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G25" s="16" t="n">
         <v>3400</v>
       </c>
     </row>
@@ -27642,7 +27352,7 @@
       <c r="D26" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27667,7 +27377,7 @@
       <c r="D27" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27692,7 +27402,7 @@
       <c r="D28" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27703,89 +27413,89 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="16" t="n">
         <v>4050</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="16" t="n">
         <v>4400</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>2025-07-27</t>
         </is>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G31" s="16" t="n">
         <v>3650</v>
       </c>
     </row>
@@ -27804,7 +27514,7 @@
       <c r="D32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27829,7 +27539,7 @@
       <c r="D33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27854,7 +27564,7 @@
       <c r="D34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27879,7 +27589,7 @@
       <c r="D35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27890,60 +27600,60 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n">
+      <c r="A36" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="16" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="n">
+      <c r="A37" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="16" t="n">
         <v>3700</v>
       </c>
     </row>
@@ -27962,7 +27672,7 @@
       <c r="D38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -27987,7 +27697,7 @@
       <c r="D39" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28012,7 +27722,7 @@
       <c r="D40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28023,60 +27733,60 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n">
+      <c r="A41" s="16" t="n">
         <v>3000</v>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="21" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="G41" s="19" t="n">
+      <c r="G41" s="16" t="n">
         <v>4600</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n">
+      <c r="A42" s="16" t="n">
         <v>3000</v>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>بدون قانون ۷</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D42" s="20" t="n">
+      <c r="D42" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="G42" s="19" t="n">
+      <c r="G42" s="16" t="n">
         <v>4950</v>
       </c>
     </row>
@@ -28095,7 +27805,7 @@
       <c r="D43" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28120,7 +27830,7 @@
       <c r="D44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28145,7 +27855,7 @@
       <c r="D45" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28170,7 +27880,7 @@
       <c r="D46" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28195,7 +27905,7 @@
       <c r="D47" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28206,31 +27916,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n">
+      <c r="A48" s="16" t="n">
         <v>3000</v>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>با قانون ۷</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="D48" s="20" t="n">
+      <c r="D48" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E48" s="21" t="inlineStr">
+      <c r="E48" s="18" t="inlineStr">
         <is>
           <t>صفر شد</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="G48" s="16" t="n">
         <v>5100</v>
       </c>
     </row>
@@ -28249,7 +27959,7 @@
       <c r="D49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28274,7 +27984,7 @@
       <c r="D50" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="E50" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28299,7 +28009,7 @@
       <c r="D51" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28324,7 +28034,7 @@
       <c r="D52" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28349,7 +28059,7 @@
       <c r="D53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E53" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28374,7 +28084,7 @@
       <c r="D54" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="E54" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28399,7 +28109,7 @@
       <c r="D55" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E55" s="22" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28424,7 +28134,7 @@
       <c r="D56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E56" s="22" t="inlineStr">
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28449,7 +28159,7 @@
       <c r="D57" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28474,7 +28184,7 @@
       <c r="D58" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28499,7 +28209,7 @@
       <c r="D59" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28524,7 +28234,7 @@
       <c r="D60" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E60" s="22" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
@@ -28549,7 +28259,7 @@
       <c r="D61" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>دوام آورد</t>
         </is>
